--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -38311,7 +38311,7 @@
       </c>
       <c r="E82" s="52" t="inlineStr">
         <is>
-          <t>運営スタッフ追加</t>
+          <t>運営スタッフ招待</t>
         </is>
       </c>
       <c r="F82" s="52" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="I82" s="52" t="inlineStr">
         <is>
-          <t>OperatorCreateRequest</t>
+          <t>OperatorInviteRequest</t>
         </is>
       </c>
       <c r="J82" s="52" t="inlineStr">
@@ -38351,7 +38351,7 @@
       </c>
       <c r="M82" s="52" t="inlineStr">
         <is>
-          <t>既存ユーザーのglobalRoleをoperator/root_operatorに変更し運営スタッフとして登録。</t>
+          <t>メールアドレスで運営スタッフを招待。Keycloakにユーザーを作成しパスワード設定リンク付き招待メールを送信。globalRoleをoperator/root_operatorに設定。learner/instructorからの昇格ではなく、新規の運営スタッフ専用アカウントを作成する。招待メール送信元はTBD。</t>
         </is>
       </c>
     </row>
@@ -40168,7 +40168,7 @@
       </c>
       <c r="E46" s="36" t="inlineStr">
         <is>
-          <t>運営スタッフ管理</t>
+          <t>メール招待による運営スタッフ追加。root_operatorがメールアドレスと付与ロール(operator/root_operator)を指定して招待メールを送信。招待されたユーザーはauth.adapt-co.io(Keycloak)でアカウント作成・パスワード設定を行いログイン可能となる。learner/instructorからの昇格ではない。</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -37921,7 +37921,7 @@
       </c>
       <c r="E76" s="49" t="inlineStr">
         <is>
-          <t>ユーザー作成（受講者/講師）</t>
+          <t>ユーザー招待（受講者/講師）</t>
         </is>
       </c>
       <c r="F76" s="48" t="inlineStr">
@@ -37941,12 +37941,12 @@
       </c>
       <c r="I76" s="50" t="inlineStr">
         <is>
-          <t>UserCreateRequest</t>
+          <t>UserInviteRequest</t>
         </is>
       </c>
       <c r="J76" s="50" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>UserAdminView</t>
         </is>
       </c>
       <c r="K76" s="50" t="inlineStr">
@@ -37961,7 +37961,7 @@
       </c>
       <c r="M76" s="50" t="inlineStr">
         <is>
-          <t>運営による受講者/講師の代理登録。globalRoleはlearnerまたはinstructorのみ指定可能。</t>
+          <t>メールアドレスで受講者/講師を招待。Keycloakにユーザー作成し招待メール送信。globalRoleはlearner/instructorのみ。operator/root_operatorは /operators 経由。招待フローは運営スタッフ招待（API-ADMIN-16）と同一方式。UI: ADM-UI-03/ADM-UI-05のモーダルダイアログから呼び出す。</t>
         </is>
       </c>
     </row>
@@ -40008,7 +40008,7 @@
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>全受講者リスト、凍結</t>
+          <t>全受講者リスト、凍結。「受講者を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="E43" s="36" t="inlineStr">
         <is>
-          <t>全講師リスト、審査</t>
+          <t>全講師リスト、審査。「講師を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -27311,7 +27311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="77.1640625" customWidth="1" min="4" max="4"/>
@@ -27398,6 +27398,33 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>06_API一覧: API-ADMIN-22（ダッシュボードKPI集計）、API-ADMIN-23（売上推移チャートデータ）、API-ADMIN-24（最近のアクティビティ）を新規追加。07_画面一覧: ADM-UI-02のdescriptionを具体化（使用API明記）。openapi_admin.yaml との整合性確保。</t>
+        </is>
+      </c>
+      <c r="E4" s="40" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="8" t="n"/>
@@ -27950,6 +27977,20 @@
       <c r="C91" s="40" t="n"/>
       <c r="D91" s="40" t="n"/>
       <c r="E91" s="40" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="40" t="n"/>
+      <c r="B92" s="40" t="n"/>
+      <c r="C92" s="40" t="n"/>
+      <c r="D92" s="40" t="n"/>
+      <c r="E92" s="40" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="40" t="n"/>
+      <c r="B93" s="40" t="n"/>
+      <c r="C93" s="40" t="n"/>
+      <c r="D93" s="40" t="n"/>
+      <c r="E93" s="40" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33006,7 +33047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -38677,6 +38718,201 @@
       <c r="M87" s="52" t="inlineStr">
         <is>
           <t>チャンネルの凍結を解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="52" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="52" t="inlineStr">
+        <is>
+          <t>API-ADMIN-22</t>
+        </is>
+      </c>
+      <c r="C88" s="52" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/dashboard/kpi</t>
+        </is>
+      </c>
+      <c r="D88" s="52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E88" s="52" t="inlineStr">
+        <is>
+          <t>ダッシュボードKPI集計</t>
+        </is>
+      </c>
+      <c r="F88" s="52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G88" s="52" t="inlineStr">
+        <is>
+          <t>operator, root_operator</t>
+        </is>
+      </c>
+      <c r="H88" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="52" t="inlineStr">
+        <is>
+          <t>DashboardKpiResponse</t>
+        </is>
+      </c>
+      <c r="K88" s="52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L88" s="52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M88" s="52" t="inlineStr">
+        <is>
+          <t>受講者数・講師数・講座数・今月売上と前月比・直近推移を返す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="52" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="52" t="inlineStr">
+        <is>
+          <t>API-ADMIN-23</t>
+        </is>
+      </c>
+      <c r="C89" s="52" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/dashboard/revenue-chart</t>
+        </is>
+      </c>
+      <c r="D89" s="52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E89" s="52" t="inlineStr">
+        <is>
+          <t>売上推移チャートデータ</t>
+        </is>
+      </c>
+      <c r="F89" s="52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G89" s="52" t="inlineStr">
+        <is>
+          <t>operator, root_operator</t>
+        </is>
+      </c>
+      <c r="H89" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="52" t="inlineStr">
+        <is>
+          <t>RevenueChartResponse</t>
+        </is>
+      </c>
+      <c r="K89" s="52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L89" s="52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M89" s="52" t="inlineStr">
+        <is>
+          <t>指定期間（7D/1M/6M/1Y）の売上推移データポイントを返す。query: period（必須）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="52" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="52" t="inlineStr">
+        <is>
+          <t>API-ADMIN-24</t>
+        </is>
+      </c>
+      <c r="C90" s="52" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/dashboard/activities</t>
+        </is>
+      </c>
+      <c r="D90" s="52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E90" s="52" t="inlineStr">
+        <is>
+          <t>最近のアクティビティ（監査ログ）</t>
+        </is>
+      </c>
+      <c r="F90" s="52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G90" s="52" t="inlineStr">
+        <is>
+          <t>operator, root_operator</t>
+        </is>
+      </c>
+      <c r="H90" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="52" t="inlineStr">
+        <is>
+          <t>DashboardActivitiesResponse</t>
+        </is>
+      </c>
+      <c r="K90" s="52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L90" s="52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M90" s="52" t="inlineStr">
+        <is>
+          <t>直近の監査ログをoccurredAt降順で返す。query: limit（任意、デフォルト10）。</t>
         </is>
       </c>
     </row>
@@ -39976,7 +40212,7 @@
       </c>
       <c r="E40" s="36" t="inlineStr">
         <is>
-          <t>サマリー、最近のアクティビティ、通知</t>
+          <t>KPI集計（受講者数・講師数・講座数・今月売上）、売上推移チャート（7D/1M/6M/1Y切替）、承認待ち講座リスト、最近のアクティビティ（監査ログ）。API: API-ADMIN-22（KPI）、API-ADMIN-23（売上推移）、API-ADMIN-24（アクティビティ）、API-ADMIN-01（承認待ち講座）。</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -1014,11 +1014,6 @@
           <t>モデル数</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>26モデル</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1064,7 +1059,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>openapi_app.yaml（50パス、64エンドポイント）</t>
+          <t>openapi_app.yaml</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>openapi_admin.yaml（15パス、21エンドポイント）</t>
+          <t>openapi_admin.yaml</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1083,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>schema.prisma（26モデル、18 Enum）</t>
+          <t>schema.prisma</t>
         </is>
       </c>
     </row>
@@ -28096,7 +28091,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>3. 主要モデル（27モデル）</t>
+          <t>3. 主要モデル</t>
         </is>
       </c>
     </row>
@@ -32842,7 +32837,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>packages/shared に全130件の Zod Schema / DTO を配置し、Next/Nest両方で利用。</t>
+          <t>packages/shared に Zod Schema / DTO を配置し、Next/Nest両方で利用。</t>
         </is>
       </c>
     </row>
@@ -33004,7 +32999,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>│           ├── dtos/       # API Request/Response 型定義 (130件分)</t>
+          <t>│           ├── dtos/       # API Request/Response 型定義</t>
         </is>
       </c>
     </row>

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -1281,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1913,370 +1913,370 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CourseStyle</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>コーススタイル（one_on_one/seminar/bootcamp/lecture）。CourseStyle enum。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>course_member</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>コースメンバー</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>コースメンバーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
+          <t>course_id</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>コースID</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>ユーザーID</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="C34" s="40" t="inlineStr">
+    <row r="35">
+      <c r="C35" s="40" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="D34" s="40" t="inlineStr">
+      <c r="D35" s="40" t="inlineStr">
         <is>
           <t>CourseMemberRole</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="E35" s="40" t="inlineStr">
         <is>
           <t>default: learner</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F35" s="40" t="inlineStr">
         <is>
           <t>コースメンバーロール（CourseMemberRole enum）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>default: now()</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>lesson</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>レッスン</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>レッスンID</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
+          <t>course_id</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>コースID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="40" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="40" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D41" s="40" t="inlineStr">
+      <c r="D42" s="40" t="inlineStr">
         <is>
           <t>LessonType</t>
         </is>
       </c>
-      <c r="E41" s="40" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
         <is>
           <t>default: text</t>
         </is>
       </c>
-      <c r="F41" s="40" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>レッスン種別（LessonType enum）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>default: now()</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>course_section_id</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Nullable, FK: course_section.id</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>所属セクションID。ブートキャンプのみ使用（1on1/セミナーはNULL）。onDelete: SetNull。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>assignment</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>課題</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>課題ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>コースID</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>タイトル</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2286,298 +2286,298 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@db.Text, Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
-          <t>due_at</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>提出期限</t>
+          <t>タイトル</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="C50" t="inlineStr">
         <is>
-          <t>allow_resubmission</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>@db.Text, Nullable</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>再提出許可</t>
+          <t>説明</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>is_published</t>
+          <t>due_at</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>公開状態</t>
+          <t>提出期限</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="C52" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>allow_resubmission</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>再提出許可</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="C53" t="inlineStr">
         <is>
+          <t>is_published</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>default: false</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>公開状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>course_channel</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>チャンネル</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>チャンネルID</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>コースID</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" s="40" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>CourseChannelType</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="40" t="inlineStr">
-        <is>
-          <t>チャンネル種別（CourseChannelType enum）</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="C58" t="inlineStr">
         <is>
-          <t>is_frozen</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>isFrozen</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="C59" s="40" t="inlineStr">
         <is>
-          <t>posting_mode</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D59" s="40" t="inlineStr">
         <is>
-          <t>CourseChannelPostingMode</t>
+          <t>CourseChannelType</t>
         </is>
       </c>
       <c r="E59" s="40" t="inlineStr">
         <is>
-          <t>default: mixed</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F59" s="40" t="inlineStr">
         <is>
-          <t>投稿モード（CourseChannelPostingMode enum）</t>
+          <t>チャンネル種別（CourseChannelType enum）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="C60" t="inlineStr">
         <is>
-          <t>frozen_at</t>
+          <t>is_frozen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>frozenAt</t>
+          <t>isFrozen</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="C61" s="40" t="inlineStr">
         <is>
-          <t>visibility</t>
+          <t>posting_mode</t>
         </is>
       </c>
       <c r="D61" s="40" t="inlineStr">
         <is>
-          <t>CourseVisibility</t>
+          <t>CourseChannelPostingMode</t>
         </is>
       </c>
       <c r="E61" s="40" t="inlineStr">
         <is>
-          <t>default: public</t>
+          <t>default: mixed</t>
         </is>
       </c>
       <c r="F61" s="40" t="inlineStr">
         <is>
-          <t>チャンネル公開設定（CourseVisibility enum）</t>
+          <t>投稿モード（CourseChannelPostingMode enum）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="C62" t="inlineStr">
         <is>
-          <t>frozen_by_user_id</t>
+          <t>frozen_at</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2587,36 +2587,36 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>frozenByUserId</t>
+          <t>frozenAt</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>freeze_reason</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>freezeReason</t>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>visibility</t>
+        </is>
+      </c>
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>CourseVisibility</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
+        <is>
+          <t>default: public</t>
+        </is>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>チャンネル公開設定（CourseVisibility enum）</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="C64" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>frozen_by_user_id</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2631,36 +2631,36 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>チャンネル名</t>
+          <t>frozenByUserId</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="C65" t="inlineStr">
         <is>
-          <t>is_manual</t>
+          <t>freeze_reason</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>手動作成フラグ</t>
+          <t>freezeReason</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" t="inlineStr">
         <is>
-          <t>system_key</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2675,200 +2675,200 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>システム識別子</t>
+          <t>チャンネル名</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="C67" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_manual</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>手動作成フラグ</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="C68" t="inlineStr">
         <is>
+          <t>system_key</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>システム識別子</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="24" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
         <is>
           <t>course_channel_member</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B72" s="24" t="inlineStr">
         <is>
           <t>チャンネルメンバー</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>チャンネルメンバーID</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="C71" t="inlineStr">
+    <row r="73">
+      <c r="C73" t="inlineStr">
         <is>
           <t>channel_id</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>チャンネルID</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>course_member_id</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>コースメンバーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="C73" s="40" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D73" s="40" t="inlineStr">
-        <is>
-          <t>CourseChannelMemberStatus</t>
-        </is>
-      </c>
-      <c r="E73" s="40" t="inlineStr">
-        <is>
-          <t>default: invited</t>
-        </is>
-      </c>
-      <c r="F73" s="40" t="inlineStr">
-        <is>
-          <t>チャンネルメンバーステータス（CourseChannelMemberStatus enum）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="C74" t="inlineStr">
         <is>
-          <t>invited_at</t>
+          <t>course_member_id</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>招待日時</t>
+          <t>コースメンバーID</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>joined_at</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>参加日時</t>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D75" s="40" t="inlineStr">
+        <is>
+          <t>CourseChannelMemberStatus</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
+        <is>
+          <t>default: invited</t>
+        </is>
+      </c>
+      <c r="F75" s="40" t="inlineStr">
+        <is>
+          <t>チャンネルメンバーステータス（CourseChannelMemberStatus enum）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="C76" t="inlineStr">
         <is>
-          <t>declined_at</t>
+          <t>invited_at</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2883,19 +2883,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>辞退日時</t>
+          <t>招待日時</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="C77" t="inlineStr">
         <is>
-          <t>last_read_message_id</t>
+          <t>joined_at</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>最終既読メッセージID</t>
+          <t>参加日時</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="C78" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>declined_at</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2922,259 +2922,259 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>辞退日時</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="C79" t="inlineStr">
         <is>
+          <t>last_read_message_id</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>最終既読メッセージID</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="24" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t>course_thread</t>
         </is>
       </c>
-      <c r="B81" s="24" t="inlineStr">
+      <c r="B83" s="24" t="inlineStr">
         <is>
           <t>スレッド</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>スレッドID</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="C82" t="inlineStr">
+    <row r="84">
+      <c r="C84" t="inlineStr">
         <is>
           <t>channel_id</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>チャンネルID</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>root_message_id</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Unique, Nullable</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>ルートメッセージID</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84" s="40" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D84" s="40" t="inlineStr">
-        <is>
-          <t>CourseThreadType</t>
-        </is>
-      </c>
-      <c r="E84" s="40" t="inlineStr">
-        <is>
-          <t>default: message_thread</t>
-        </is>
-      </c>
-      <c r="F84" s="40" t="inlineStr">
-        <is>
-          <t>スレッド種別（CourseThreadType enum）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="C85" t="inlineStr">
         <is>
+          <t>root_message_id</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Unique, Nullable</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ルートメッセージID</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" s="40" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D86" s="40" t="inlineStr">
+        <is>
+          <t>CourseThreadType</t>
+        </is>
+      </c>
+      <c r="E86" s="40" t="inlineStr">
+        <is>
+          <t>default: message_thread</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr">
+        <is>
+          <t>スレッド種別（CourseThreadType enum）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="C86" t="inlineStr">
+    <row r="88">
+      <c r="C88" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="24" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>course_thread_read_state</t>
         </is>
       </c>
-      <c r="B88" s="24" t="inlineStr">
+      <c r="B90" s="24" t="inlineStr">
         <is>
           <t>スレッド既読状態</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>既読状態ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>thread_id</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>スレッドID</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>course_member_id</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>コースメンバーID</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="C91" t="inlineStr">
         <is>
-          <t>last_read_message_id</t>
+          <t>thread_id</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3184,139 +3184,139 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>最終既読メッセージID</t>
+          <t>スレッドID</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="C92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>course_member_id</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>コースメンバーID</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="C93" t="inlineStr">
         <is>
+          <t>last_read_message_id</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>最終既読メッセージID</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="24" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="24" t="inlineStr">
         <is>
           <t>course_message</t>
         </is>
       </c>
-      <c r="B95" s="24" t="inlineStr">
+      <c r="B97" s="24" t="inlineStr">
         <is>
           <t>メッセージ</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>メッセージID</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>channel_id</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>チャンネルID</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>thread_id</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>スレッドID（root messages: null; replies: set）</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="C98" t="inlineStr">
         <is>
-          <t>author_course_member_id</t>
+          <t>channel_id</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3326,19 +3326,19 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>投稿者（コースメンバーID）</t>
+          <t>チャンネルID</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="C99" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>thread_id</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3348,161 +3348,161 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>スレッドID（root messages: null; replies: set）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="C100" t="inlineStr">
         <is>
-          <t>is_emergency</t>
+          <t>author_course_member_id</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>緊急フラグ</t>
+          <t>投稿者（コースメンバーID）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="C101" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>本文</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="C102" t="inlineStr">
         <is>
+          <t>is_emergency</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>default: false</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>緊急フラグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="24" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="24" t="inlineStr">
         <is>
           <t>course_message_attachment</t>
         </is>
       </c>
-      <c r="B104" s="24" t="inlineStr">
+      <c r="B106" s="24" t="inlineStr">
         <is>
           <t>メッセージ添付</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>添付ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>course_message_id</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>メッセージID</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>ファイル種別（image / file / pdf / etc）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="C107" t="inlineStr">
         <is>
-          <t>storage_key</t>
+          <t>course_message_id</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>外部ストレージキー（例：S3）</t>
+          <t>メッセージID</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="C108" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3539,14 +3539,14 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ファイル名</t>
+          <t>ファイル種別（image / file / pdf / etc）</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="C109" t="inlineStr">
         <is>
-          <t>mime_type</t>
+          <t>storage_key</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3561,19 +3561,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIMEタイプ</t>
+          <t>外部ストレージキー（例：S3）</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="C110" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3583,134 +3583,134 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ファイルサイズ（バイト）</t>
+          <t>ファイル名</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="C111" t="inlineStr">
         <is>
+          <t>mime_type</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MIMEタイプ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ファイルサイズ（バイト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="24" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="24" t="inlineStr">
         <is>
           <t>course_notification_preference</t>
         </is>
       </c>
-      <c r="B113" s="24" t="inlineStr">
+      <c r="B115" s="24" t="inlineStr">
         <is>
           <t>コース通知設定</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>通知設定ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>course_member_id</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>コースメンバーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>announcement_normal_enabled</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>default: true</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>通常アナウンス通知</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="C116" t="inlineStr">
         <is>
-          <t>submission_enabled</t>
+          <t>course_member_id</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>default: true</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>提出通知（講師向け）</t>
+          <t>コースメンバーID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="C117" t="inlineStr">
         <is>
-          <t>submission_comment_enabled</t>
+          <t>announcement_normal_enabled</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3725,14 +3725,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>提出コメント通知（受講者向け）</t>
+          <t>通常アナウンス通知</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="C118" t="inlineStr">
         <is>
-          <t>thread_reply_enabled</t>
+          <t>submission_enabled</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3747,342 +3747,342 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>スレッド返信通知（フォロー中のみ）</t>
+          <t>提出通知（講師向け）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="C119" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>submission_comment_enabled</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>default: true</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>提出コメント通知（受講者向け）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="C120" t="inlineStr">
         <is>
+          <t>thread_reply_enabled</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>default: true</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>スレッド返信通知（フォロー中のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="24" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="24" t="inlineStr">
         <is>
           <t>course_channel_notification_preference</t>
         </is>
       </c>
-      <c r="B122" s="24" t="inlineStr">
+      <c r="B124" s="24" t="inlineStr">
         <is>
           <t>チャンネル通知設定</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>通知設定ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>course_member_id</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>コースメンバーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>channel_id</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>チャンネルID</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="C125" t="inlineStr">
         <is>
-          <t>muted</t>
+          <t>course_member_id</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ミュート</t>
+          <t>コースメンバーID</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="C126" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>channel_id</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>チャンネルID</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="C127" t="inlineStr">
         <is>
+          <t>muted</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>default: false</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ミュート</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="24" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="24" t="inlineStr">
         <is>
           <t>course_enrollment</t>
         </is>
       </c>
-      <c r="B129" s="24" t="inlineStr">
+      <c r="B131" s="24" t="inlineStr">
         <is>
           <t>受講権限</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>受講権限ID</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="C130" t="inlineStr">
+    <row r="132">
+      <c r="C132" t="inlineStr">
         <is>
           <t>course_id</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>コースID</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="C132" s="40" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D132" s="40" t="inlineStr">
-        <is>
-          <t>CourseEnrollmentStatus</t>
-        </is>
-      </c>
-      <c r="E132" s="40" t="inlineStr">
-        <is>
-          <t>default: applied</t>
-        </is>
-      </c>
-      <c r="F132" s="40" t="inlineStr">
-        <is>
-          <t>受講ステータス（CourseEnrollmentStatus enum）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="C133" t="inlineStr">
         <is>
-          <t>granted_at</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>受講付与日時</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="C134" s="40" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D134" s="40" t="inlineStr">
         <is>
-          <t>PaymentProvider</t>
+          <t>CourseEnrollmentStatus</t>
         </is>
       </c>
       <c r="E134" s="40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>default: applied</t>
         </is>
       </c>
       <c r="F134" s="40" t="inlineStr">
         <is>
-          <t>受講権付与元（stripe/manual）</t>
+          <t>受講ステータス（CourseEnrollmentStatus enum）</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="C135" t="inlineStr">
         <is>
-          <t>revoked_at</t>
+          <t>granted_at</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4097,41 +4097,41 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>受講取り消し日時</t>
+          <t>受講付与日時</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>paid_at</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>支払い完了日時</t>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D136" s="40" t="inlineStr">
+        <is>
+          <t>PaymentProvider</t>
+        </is>
+      </c>
+      <c r="E136" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="inlineStr">
+        <is>
+          <t>受講権付与元（stripe/manual）</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="C137" t="inlineStr">
         <is>
-          <t>payment_id</t>
+          <t>revoked_at</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>決済ID</t>
+          <t>受講取り消し日時</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="C138" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>paid_at</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4158,117 +4158,117 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>支払い完了日時</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="C139" t="inlineStr">
         <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>決済ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="24" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="24" t="inlineStr">
         <is>
           <t>payment</t>
         </is>
       </c>
-      <c r="B141" s="24" t="inlineStr">
+      <c r="B143" s="24" t="inlineStr">
         <is>
           <t>決済</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>決済ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>provider_ref</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Unique, Nullable</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>事業者識別子</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="C144" t="inlineStr">
         <is>
-          <t>course_id</t>
+          <t>provider_ref</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>Unique, Nullable</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>コースID</t>
+          <t>事業者識別子</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="C145" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>金額</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="C146" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4322,210 +4322,210 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>コースID</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>通貨</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="C147" s="40" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="D147" s="40" t="inlineStr">
-        <is>
-          <t>PaymentProvider</t>
-        </is>
-      </c>
-      <c r="E147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" s="40" t="inlineStr">
-        <is>
-          <t>決済事業者（PaymentProvider enum）</t>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>金額</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="C148" t="inlineStr">
         <is>
-          <t>paid_at</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>支払い完了日時</t>
+          <t>通貨</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="C149" s="40" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="D149" s="40" t="inlineStr">
         <is>
-          <t>PaymentStatus</t>
+          <t>PaymentProvider</t>
         </is>
       </c>
       <c r="E149" s="40" t="inlineStr">
         <is>
-          <t>default: pending</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F149" s="40" t="inlineStr">
         <is>
-          <t>決済ステータス（PaymentStatus enum）</t>
+          <t>決済事業者（PaymentProvider enum）</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="C150" t="inlineStr">
         <is>
+          <t>paid_at</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>支払い完了日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="C151" s="40" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D151" s="40" t="inlineStr">
+        <is>
+          <t>PaymentStatus</t>
+        </is>
+      </c>
+      <c r="E151" s="40" t="inlineStr">
+        <is>
+          <t>default: pending</t>
+        </is>
+      </c>
+      <c r="F151" s="40" t="inlineStr">
+        <is>
+          <t>決済ステータス（PaymentStatus enum）</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="C151" t="inlineStr">
+    <row r="153">
+      <c r="C153" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="24" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="24" t="inlineStr">
         <is>
           <t>refund</t>
         </is>
       </c>
-      <c r="B153" s="24" t="inlineStr">
+      <c r="B155" s="24" t="inlineStr">
         <is>
           <t>返金</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>返金ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>決済ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>provider_ref</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Unique, Nullable</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>事業者識別子</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="C156" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>payment_id</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4535,227 +4535,227 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>返金額</t>
+          <t>決済ID</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="C157" s="40" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D157" s="40" t="inlineStr">
-        <is>
-          <t>RefundStatus</t>
-        </is>
-      </c>
-      <c r="E157" s="40" t="inlineStr">
-        <is>
-          <t>default: pending</t>
-        </is>
-      </c>
-      <c r="F157" s="40" t="inlineStr">
-        <is>
-          <t>返金ステータス（RefundStatus enum）</t>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>provider_ref</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Unique, Nullable</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>事業者識別子</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="C158" t="inlineStr">
         <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>返金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" s="40" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D159" s="40" t="inlineStr">
+        <is>
+          <t>RefundStatus</t>
+        </is>
+      </c>
+      <c r="E159" s="40" t="inlineStr">
+        <is>
+          <t>default: pending</t>
+        </is>
+      </c>
+      <c r="F159" s="40" t="inlineStr">
+        <is>
+          <t>返金ステータス（RefundStatus enum）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="C159" t="inlineStr">
+    <row r="161">
+      <c r="C161" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="24" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="24" t="inlineStr">
         <is>
           <t>coupon</t>
         </is>
       </c>
-      <c r="B161" s="24" t="inlineStr">
+      <c r="B163" s="24" t="inlineStr">
         <is>
           <t>クーポン</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>クーポンID</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>クーポンコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="C163" s="40" t="inlineStr">
-        <is>
-          <t>discount_type</t>
-        </is>
-      </c>
-      <c r="D163" s="40" t="inlineStr">
-        <is>
-          <t>CouponDiscountType</t>
-        </is>
-      </c>
-      <c r="E163" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" s="40" t="inlineStr">
-        <is>
-          <t>クーポン割引種別（CouponDiscountType enum）</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="C164" t="inlineStr">
         <is>
-          <t>discount_value</t>
+          <t>code</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>クーポンコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="C165" s="40" t="inlineStr">
+        <is>
+          <t>discount_type</t>
+        </is>
+      </c>
+      <c r="D165" s="40" t="inlineStr">
+        <is>
+          <t>CouponDiscountType</t>
+        </is>
+      </c>
+      <c r="E165" s="40" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>割引値</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>通貨</t>
+      <c r="F165" s="40" t="inlineStr">
+        <is>
+          <t>クーポン割引種別（CouponDiscountType enum）</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="C166" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>discount_value</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>有効期限</t>
+          <t>割引値</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="C167" t="inlineStr">
         <is>
-          <t>usage_limit</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4765,178 +4765,178 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>利用上限</t>
+          <t>通貨</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="C168" t="inlineStr">
         <is>
-          <t>used_count</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>利用済み回数</t>
+          <t>有効期限</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="C169" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>usage_limit</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>default: true</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>有効フラグ</t>
+          <t>利用上限</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="C170" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>used_count</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>利用済み回数</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="C171" t="inlineStr">
         <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>default: true</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>有効フラグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="C173" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="24" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="24" t="inlineStr">
         <is>
           <t>coupon_redemption</t>
         </is>
       </c>
-      <c r="B173" s="24" t="inlineStr">
+      <c r="B175" s="24" t="inlineStr">
         <is>
           <t>クーポン利用</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>利用ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>coupon_id</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>クーポンID</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="C176" t="inlineStr">
         <is>
-          <t>course_id</t>
+          <t>coupon_id</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4946,19 +4946,19 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>コースID</t>
+          <t>クーポンID</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="C177" t="inlineStr">
         <is>
-          <t>payment_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4968,188 +4968,188 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>決済ID</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="C178" t="inlineStr">
         <is>
-          <t>redeemed_at</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>利用日時</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="C179" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>payment_id</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>決済ID</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="C180" t="inlineStr">
         <is>
+          <t>redeemed_at</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>利用日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="C182" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="24" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="24" t="inlineStr">
         <is>
           <t>audit_event</t>
         </is>
       </c>
-      <c r="B182" s="24" t="inlineStr">
+      <c r="B184" s="24" t="inlineStr">
         <is>
           <t>監査イベント</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>イベントID</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="C183" t="inlineStr">
+    <row r="185">
+      <c r="C185" t="inlineStr">
         <is>
           <t>occurred_at</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>発生日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>actor_user_id</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>実行者ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="C185" s="40" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="D185" s="40" t="inlineStr">
-        <is>
-          <t>AuditEventType</t>
-        </is>
-      </c>
-      <c r="E185" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F185" s="40" t="inlineStr">
-        <is>
-          <t>監査イベント種別（AuditEventType enum）</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="C186" t="inlineStr">
         <is>
-          <t>actor_global_role</t>
+          <t>actor_user_id</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>GlobalRole</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5159,58 +5159,58 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>操作時のGlobalRole（操作者の権限を記録）</t>
+          <t>実行者ID</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>コースID</t>
+      <c r="C187" s="40" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="D187" s="40" t="inlineStr">
+        <is>
+          <t>AuditEventType</t>
+        </is>
+      </c>
+      <c r="E187" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" s="40" t="inlineStr">
+        <is>
+          <t>監査イベント種別（AuditEventType enum）</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="C188" t="inlineStr">
         <is>
-          <t>channel_id</t>
+          <t>actor_global_role</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>GlobalRole</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>チャンネルID</t>
+          <t>操作時のGlobalRole（操作者の権限を記録）</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="C189" t="inlineStr">
         <is>
-          <t>message_id</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>メッセージID</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="C190" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>channel_id</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5242,24 +5242,24 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>チャンネルID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="C191" t="inlineStr">
         <is>
-          <t>meta_json</t>
+          <t>message_id</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5269,14 +5269,14 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>メタデータ</t>
+          <t>メッセージID</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="C192" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5286,24 +5286,24 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>リクエストID</t>
+          <t>理由</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="C193" t="inlineStr">
         <is>
-          <t>ip_hash</t>
+          <t>meta_json</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>json</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5313,14 +5313,14 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IPハッシュ</t>
+          <t>メタデータ</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="C194" t="inlineStr">
         <is>
-          <t>user_agent_hash</t>
+          <t>request_id</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5335,139 +5335,139 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>UserAgentハッシュ</t>
+          <t>リクエストID</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="C195" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>ip_hash</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>IPハッシュ</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="C196" t="inlineStr">
         <is>
+          <t>user_agent_hash</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>UserAgentハッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="C198" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="24" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="24" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B198" s="24" t="inlineStr">
+      <c r="B200" s="24" t="inlineStr">
         <is>
           <t>注文</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>注文ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="C201" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5477,14 +5477,14 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>支払金額（0可）</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="C202" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5499,19 +5499,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>通貨（JPY など）</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="C203" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>OrderStatus</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5521,14 +5521,14 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ステータス（paid / refunded / canceled）</t>
+          <t>支払金額（0可）</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="C204" t="inlineStr">
         <is>
-          <t>payment_provider</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5543,134 +5543,134 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>決済事業者（stripe）</t>
+          <t>通貨（JPY など）</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="C205" t="inlineStr">
         <is>
-          <t>payment_intent_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>OrderStatus</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Stripe PaymentIntent ID</t>
+          <t>ステータス（paid / refunded / canceled）</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="C206" t="inlineStr">
         <is>
+          <t>payment_provider</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>決済事業者（stripe）</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>payment_intent_id</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Stripe PaymentIntent ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="C208" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="24" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="24" t="inlineStr">
         <is>
           <t>o_auth_identity</t>
         </is>
       </c>
-      <c r="B208" s="24" t="inlineStr">
+      <c r="B210" s="24" t="inlineStr">
         <is>
           <t>OAuth認証</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>認証情報ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>プロバイダ（google / apple / internal / line / etc）</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="C211" t="inlineStr">
         <is>
-          <t>provider_user_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5685,14 +5685,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>プロバイダ側のユーザーID（sub / OIDC subject）</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="C212" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5702,139 +5702,139 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>プロバイダ（google / apple / internal / line / etc）</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="C213" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>provider_user_id</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>最終ログイン日時</t>
+          <t>プロバイダ側のユーザーID（sub / OIDC subject）</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="C214" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>last_login_at</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>最終ログイン日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="C216" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="24" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="24" t="inlineStr">
         <is>
           <t>password_credential</t>
         </is>
       </c>
-      <c r="B216" s="24" t="inlineStr">
+      <c r="B218" s="24" t="inlineStr">
         <is>
           <t>パスワード認証</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>認証情報ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>password_hash</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>パスワードハッシュ</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="C219" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5844,24 +5844,24 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>アルゴリズム（bcrypt / argon2id 等）</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="C220" t="inlineStr">
         <is>
-          <t>password_updated_at</t>
+          <t>password_hash</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5871,41 +5871,41 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>パスワード更新日時</t>
+          <t>パスワードハッシュ</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="C221" t="inlineStr">
         <is>
-          <t>is_disabled</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>無効化フラグ</t>
+          <t>アルゴリズム（bcrypt / argon2id 等）</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="C222" t="inlineStr">
         <is>
-          <t>failed_count</t>
+          <t>password_updated_at</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5915,156 +5915,156 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>失敗回数</t>
+          <t>パスワード更新日時</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="C223" t="inlineStr">
         <is>
-          <t>last_failed_at</t>
+          <t>is_disabled</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>最終失敗日時</t>
+          <t>無効化フラグ</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="C224" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>failed_count</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>失敗回数</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="C225" t="inlineStr">
         <is>
+          <t>last_failed_at</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>最終失敗日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="C227" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="24" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="24" t="inlineStr">
         <is>
           <t>file_object</t>
         </is>
       </c>
-      <c r="B227" s="24" t="inlineStr">
+      <c r="B229" s="24" t="inlineStr">
         <is>
           <t>ファイルオブジェクト</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>ファイルID</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>storage_key</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>S3 等のキー</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>bucket</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>バケット名</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="C230" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>storage_key</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6074,19 +6074,19 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ファイル名</t>
+          <t>S3 等のキー</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="C231" t="inlineStr">
         <is>
-          <t>mime_type</t>
+          <t>bucket</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6101,19 +6101,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>MIMEタイプ</t>
+          <t>バケット名</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="C232" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6123,14 +6123,14 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ファイルサイズ（バイト）</t>
+          <t>ファイル名</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="C233" t="inlineStr">
         <is>
-          <t>checksum</t>
+          <t>mime_type</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6140,205 +6140,205 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>チェックサム（sha256 等）</t>
+          <t>MIMEタイプ</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="C234" t="inlineStr">
         <is>
-          <t>is_scanned</t>
+          <t>size</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>スキャン済みフラグ</t>
+          <t>ファイルサイズ（バイト）</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="C235" t="inlineStr">
         <is>
-          <t>is_malicious</t>
+          <t>checksum</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>default: false</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>マルウェアフラグ</t>
+          <t>チェックサム（sha256 等）</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="C236" t="inlineStr">
         <is>
-          <t>created_by_user_id</t>
+          <t>is_scanned</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>作成者ID</t>
+          <t>スキャン済みフラグ</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="C237" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>is_malicious</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>default: false</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>削除日時</t>
+          <t>マルウェアフラグ</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="C238" t="inlineStr">
         <is>
+          <t>created_by_user_id</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>作成者ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>削除日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="C240" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>default: now()</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="24" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="24" t="inlineStr">
         <is>
           <t>submission</t>
         </is>
       </c>
-      <c r="B240" s="24" t="inlineStr">
+      <c r="B242" s="24" t="inlineStr">
         <is>
           <t>提出</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>提出ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>課題ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="C243" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6353,14 +6353,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>提出者ID（learner）</t>
+          <t>課題ID</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="C244" t="inlineStr">
         <is>
-          <t>thread_id</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -6375,41 +6375,41 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>提出専用スレッドID</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="C245" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>提出日時</t>
+          <t>提出者ID（learner）</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="C246" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>thread_id</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SubmissionStatus</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -6419,112 +6419,112 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ステータス（submitted / resubmitted / late）</t>
+          <t>提出専用スレッドID</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="C247" t="inlineStr">
         <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>提出日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SubmissionStatus</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>ステータス（submitted / resubmitted / late）</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="C249" t="inlineStr">
+        <is>
           <t>graded_at</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>採点日時</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="24" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="24" t="inlineStr">
         <is>
           <t>user_profile</t>
         </is>
       </c>
-      <c r="B249" s="24" t="inlineStr">
+      <c r="B251" s="24" t="inlineStr">
         <is>
           <t>ユーザープロフィール</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>プロフィールID</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>表示名</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="C252" t="inlineStr">
         <is>
-          <t>avatar_file_object_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6534,19 +6534,19 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>アバター画像ID</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="C253" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>display_name</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6556,161 +6556,161 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>自己紹介</t>
+          <t>表示名</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="C254" t="inlineStr">
         <is>
-          <t>is_public</t>
+          <t>avatar_file_object_id</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>default: true</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>公開フラグ</t>
+          <t>アバター画像ID</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="C255" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>bio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>自己紹介</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="C256" t="inlineStr">
         <is>
+          <t>is_public</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>default: true</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>公開フラグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="C258" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="24" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="24" t="inlineStr">
         <is>
           <t>grading_comment</t>
         </is>
       </c>
-      <c r="B258" s="24" t="inlineStr">
+      <c r="B260" s="24" t="inlineStr">
         <is>
           <t>採点コメント</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>PK, default: cuid()</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>採点コメントID</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>course_id</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>コースID</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>thread_id</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>スレッドID</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="C261" t="inlineStr">
         <is>
-          <t>author_user_id</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>投稿者（instructor / assistant）</t>
+          <t>コースID</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="C262" t="inlineStr">
         <is>
-          <t>target_user_id</t>
+          <t>thread_id</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>評価対象（learner）</t>
+          <t>スレッドID</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="C263" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>author_user_id</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6764,76 +6764,262 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>@db.Text</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>コメント本文</t>
+          <t>投稿者（instructor / assistant）</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="C264" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>target_user_id</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Nullable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>数値評価（任意）</t>
+          <t>評価対象（learner）</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="C265" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>body</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>default: now()</t>
+          <t>@db.Text</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>コメント本文</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="C266" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>数値評価（任意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="C268" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>@updatedAt</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>course_section</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>コースセクション</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>PK, default: cuid()</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>セクションID</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>course_id</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>NOT NULL, FK: course.id</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>所属コースID</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>セクション名（例: Week 1, 制作準備と基礎固め）</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>表示順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>default: now()</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>@updatedAt</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
@@ -23757,7 +23943,7 @@
       </c>
       <c r="C5" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INS-UI-23</t>
         </is>
       </c>
       <c r="D5" s="55" t="inlineStr">
@@ -24068,7 +24254,7 @@
       </c>
       <c r="C14" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-02</t>
+          <t>STU-UI-02, STU-UI-14</t>
         </is>
       </c>
       <c r="D14" s="55" t="inlineStr">
@@ -24102,7 +24288,7 @@
       </c>
       <c r="C15" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-03</t>
+          <t>STU-UI-03, STU-UI-14, STU-UI-15</t>
         </is>
       </c>
       <c r="D15" s="55" t="inlineStr">
@@ -24136,7 +24322,7 @@
       </c>
       <c r="C16" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-01</t>
+          <t>STU-UI-01, STU-UI-14</t>
         </is>
       </c>
       <c r="D16" s="55" t="inlineStr">
@@ -24170,7 +24356,7 @@
       </c>
       <c r="C17" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>STU-UI-15</t>
         </is>
       </c>
       <c r="D17" s="55" t="inlineStr">
@@ -24500,7 +24686,7 @@
       </c>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-04</t>
+          <t>INS-UI-04, INS-UI-18, INS-UI-19</t>
         </is>
       </c>
       <c r="D27" s="55" t="inlineStr">
@@ -24532,7 +24718,7 @@
       </c>
       <c r="C28" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-05</t>
+          <t>INS-UI-05, INS-UI-19</t>
         </is>
       </c>
       <c r="D28" s="55" t="inlineStr">
@@ -24564,7 +24750,7 @@
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-05</t>
+          <t>INS-UI-05, INS-UI-19</t>
         </is>
       </c>
       <c r="D29" s="55" t="inlineStr">
@@ -24628,7 +24814,7 @@
       </c>
       <c r="C31" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-17</t>
+          <t>INS-UI-18, INS-UI-22</t>
         </is>
       </c>
       <c r="D31" s="55" t="inlineStr">
@@ -24660,7 +24846,7 @@
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>INS-UI-05</t>
+          <t>INS-UI-05, INS-UI-18, INS-UI-22</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
@@ -24756,7 +24942,7 @@
       </c>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-06</t>
+          <t>INS-UI-20</t>
         </is>
       </c>
       <c r="D35" s="55" t="inlineStr">
@@ -24788,7 +24974,7 @@
       </c>
       <c r="C36" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-08</t>
+          <t>INS-UI-20</t>
         </is>
       </c>
       <c r="D36" s="55" t="inlineStr">
@@ -24820,7 +25006,7 @@
       </c>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-06</t>
+          <t>INS-UI-20</t>
         </is>
       </c>
       <c r="D37" s="55" t="inlineStr">
@@ -24884,7 +25070,7 @@
       </c>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-07</t>
+          <t>INS-UI-21</t>
         </is>
       </c>
       <c r="D39" s="55" t="inlineStr">
@@ -24948,7 +25134,7 @@
       </c>
       <c r="C41" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-08</t>
+          <t>INS-UI-21</t>
         </is>
       </c>
       <c r="D41" s="55" t="inlineStr">
@@ -25044,7 +25230,7 @@
       </c>
       <c r="C44" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-10</t>
+          <t>INS-UI-10, INS-UI-24</t>
         </is>
       </c>
       <c r="D44" s="55" t="inlineStr">
@@ -25076,7 +25262,7 @@
       </c>
       <c r="C45" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-11</t>
+          <t>INS-UI-11, INS-UI-24</t>
         </is>
       </c>
       <c r="D45" s="55" t="inlineStr">
@@ -25108,7 +25294,7 @@
       </c>
       <c r="C46" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-11</t>
+          <t>INS-UI-11, INS-UI-24</t>
         </is>
       </c>
       <c r="D46" s="55" t="inlineStr">
@@ -25236,7 +25422,7 @@
       </c>
       <c r="C50" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-08</t>
+          <t>STU-UI-08, INS-UI-25, STU-UI-16</t>
         </is>
       </c>
       <c r="D50" s="55" t="inlineStr">
@@ -25364,7 +25550,7 @@
       </c>
       <c r="C54" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-07, STU-UI-09</t>
+          <t>INS-UI-21, STU-UI-09, INS-UI-25, STU-UI-16</t>
         </is>
       </c>
       <c r="D54" s="55" t="inlineStr">
@@ -25396,7 +25582,7 @@
       </c>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-09</t>
+          <t>STU-UI-09, STU-UI-16</t>
         </is>
       </c>
       <c r="D55" s="55" t="inlineStr">
@@ -25428,7 +25614,7 @@
       </c>
       <c r="C56" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-12</t>
+          <t>INS-UI-12, INS-UI-25</t>
         </is>
       </c>
       <c r="D56" s="55" t="inlineStr">
@@ -25460,7 +25646,7 @@
       </c>
       <c r="C57" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-13, STU-UI-09</t>
+          <t>INS-UI-13, STU-UI-09, INS-UI-25, STU-UI-16</t>
         </is>
       </c>
       <c r="D57" s="55" t="inlineStr">
@@ -25492,7 +25678,7 @@
       </c>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-13, STU-UI-09</t>
+          <t>INS-UI-13, STU-UI-09, INS-UI-25, STU-UI-16</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
@@ -25524,7 +25710,7 @@
       </c>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>INS-UI-13, STU-UI-09</t>
+          <t>INS-UI-13, STU-UI-09, INS-UI-25, STU-UI-16</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
@@ -38922,7 +39108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="19.33203125" customWidth="1" min="3" max="3"/>
@@ -39254,7 +39440,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-03-1</t>
+          <t>STU-UI-04</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -39264,17 +39450,17 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>講座レッスン画面</t>
+          <t>講座申込み画面</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/lessons/[lessonId]</t>
+          <t>/learner/courses/[courseId]/apply</t>
         </is>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>レッスン内容表示（動画・テキスト）</t>
+          <t>講座申込フォーム、Stripe決済</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -39286,7 +39472,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-04</t>
+          <t>STU-UI-05</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -39296,17 +39482,17 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>講座申込み画面</t>
+          <t>課題一覧</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/apply</t>
+          <t>/learner/courses/[courseId]/assignments</t>
         </is>
       </c>
       <c r="E12" s="36" t="inlineStr">
         <is>
-          <t>講座申込フォーム、Stripe決済</t>
+          <t>全課題一覧、提出状況確認</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -39318,7 +39504,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-05</t>
+          <t>STU-UI-06</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -39328,17 +39514,17 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>課題一覧</t>
+          <t>課題詳細・提出</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/assignments</t>
+          <t>/learner/courses/[courseId]/lessons/[lessonId]/assignments</t>
         </is>
       </c>
       <c r="E13" s="36" t="inlineStr">
         <is>
-          <t>全課題一覧、提出状況確認</t>
+          <t>課題内容、提出フォーム、採点結果</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -39350,7 +39536,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-06</t>
+          <t>STU-UI-07</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -39360,17 +39546,17 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>課題詳細・提出</t>
+          <t>アンケート回答</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/lessons/[lessonId]/assignments</t>
+          <t>/learner/surveys/[surveyId]</t>
         </is>
       </c>
       <c r="E14" s="36" t="inlineStr">
         <is>
-          <t>課題内容、提出フォーム、採点結果</t>
+          <t>アンケート回答フォーム</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -39382,7 +39568,7 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-07</t>
+          <t>STU-UI-08</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -39392,29 +39578,29 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>アンケート回答</t>
+          <t>講座チャット（一覧）</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>/learner/surveys/[surveyId]</t>
+          <t>/learner/courses/[courseId]/chat</t>
         </is>
       </c>
       <c r="E15" s="36" t="inlineStr">
         <is>
-          <t>アンケート回答フォーム</t>
+          <t>リアルタイムチャット、スレッド機能</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>learner</t>
+          <t>learner,instructor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-08</t>
+          <t>STU-UI-09</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -39424,12 +39610,12 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>講座チャット（一覧）</t>
+          <t>講座チャット（詳細）</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/chat</t>
+          <t>/learner/courses/[courseId]/chat/channels/[channelId]</t>
         </is>
       </c>
       <c r="E16" s="36" t="inlineStr">
@@ -39446,7 +39632,7 @@
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-09</t>
+          <t>STU-UI-10</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -39456,29 +39642,29 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>講座チャット（詳細）</t>
+          <t>実績・修了履歴</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>/learner/courses/[courseId]/chat/channels/[channelId]</t>
+          <t>/learner/records</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t>リアルタイムチャット、スレッド機能</t>
+          <t>学習履歴、修了証、統計</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>learner,instructor</t>
+          <t>learner</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-10</t>
+          <t>STU-UI-11</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -39488,29 +39674,29 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>実績・修了履歴</t>
+          <t>設定メニュー（共通）</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>/learner/records</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
         <is>
-          <t>学習履歴、修了証、統計</t>
+          <t>ログインユーザー共通の設定コンテナ。サイドメニュー（支払い/アカウント）を提供する。受講者/講師でURL分岐しない。表示項目はロールにより制御する。</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>learner</t>
+          <t>learner,instructor</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>STU-UI-11</t>
+          <t>STU-UI-12</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -39520,17 +39706,17 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>設定メニュー（共通）</t>
+          <t>アカウント設定（共通）</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>/settings</t>
+          <t>/settings/account</t>
         </is>
       </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
-          <t>ログインユーザー共通の設定コンテナ。サイドメニュー（支払い/アカウント）を提供する。受講者/講師でURL分岐しない。表示項目はロールにより制御する。</t>
+          <t>パスワード変更、通知設定、プライバシー、言語/タイムゾーン等のアカウント関連設定。講師専用項目は同一URL内でセクション表示制御。</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -39540,139 +39726,139 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>STU-UI-12</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STU-UI-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>アカウント設定（共通）</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>/settings/account</t>
-        </is>
-      </c>
-      <c r="E20" s="36" t="inlineStr">
-        <is>
-          <t>パスワード変更、通知設定、プライバシー、言語/タイムゾーン等のアカウント関連設定。講師専用項目は同一URL内でセクション表示制御。</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>learner,instructor</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STU-UI-13</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>支払い設定（共通）</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>/settings/billing</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>設定メニューの支払いタブ（共通）。
 * 支払い（受講）：全ユーザー表示。現状は決済時にStripe Checkoutで入力（支払い方法の保存管理はTBD）。
 * 受取（講師）：講師のみ表示。現状は INS-UI-15（収益管理）へ遷移（暫定導線）。将来はStripe Connectを本画面へ統合予定（TBD）。</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>learner,instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STU-UI-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ブートキャンプ受講（ホーム）</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>/learner/courses/[courseId]/bootcamp/home</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座の受講者向けホーム画面。講座固有サイドバー（ホーム/通知/カリキュラム確認/参加者一覧/コミュニティチャット）を持つ。カリキュラム進捗、通知を表示する。</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>learner,instructor</t>
+          <t>learner</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>INS-UI-01</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STU-UI-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>講師ダッシュボード</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>/instructor/dashboard</t>
-        </is>
-      </c>
-      <c r="E22" s="36" t="inlineStr">
-        <is>
-          <t>サマリー、最近のアクティビティ、通知</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>instructor</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ブートキャンプ受講（レッスン閲覧）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>/learner/courses/[courseId]/bootcamp/lessons/[lessonId]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座のレッスン閲覧画面。レッスンタイプ（座学/動画/ライブ・イベント）に応じた表示を行う。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>learner</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>INS-UI-02</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STU-UI-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>受講者管理（講師）</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>/instructor/students</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t>全受講者リスト、凍結</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>instructor</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ブートキャンプ受講（コミュニティチャット）</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>/learner/courses/[courseId]/bootcamp/chat</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座の受講者向けコミュニティチャット画面。講師側（INS-UI-25）と同じチャンネル構造で参加する。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>learner</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-03</t>
+          <t>INS-UI-01</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
@@ -39682,17 +39868,17 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>講座一覧（講師）</t>
+          <t>講師ダッシュボード</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses</t>
+          <t>/instructor/dashboard</t>
         </is>
       </c>
       <c r="E24" s="36" t="inlineStr">
         <is>
-          <t>講座一覧（講師）画面</t>
+          <t>サマリー、最近のアクティビティ、通知</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -39704,7 +39890,7 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-04</t>
+          <t>INS-UI-02</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -39714,18 +39900,17 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>講座作成</t>
+          <t>受講者管理（講師）</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/new</t>
+          <t>/instructor/students</t>
         </is>
       </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
-          <t>新規講座作成フォーム
-ブートキャンプは複数作成画面を経由し、最終的に INS-UI-17 で承認申請を実施する。</t>
+          <t>全受講者リスト、凍結</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -39737,94 +39922,94 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
+          <t>INS-UI-03</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>講座一覧（講師）</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>/instructor/courses</t>
+        </is>
+      </c>
+      <c r="E26" s="36" t="inlineStr">
+        <is>
+          <t>講座一覧（講師）画面</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>INS-UI-04</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>講座作成（スタイル選択）</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>/instructor/courses/new</t>
+        </is>
+      </c>
+      <c r="E27" s="36" t="inlineStr">
+        <is>
+          <t>講座スタイル選択画面。1on1/セミナー/ブートキャンプから選択し、スタイル別の作成画面へ遷移する。</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
           <t>INS-UI-05</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>講座編集</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>/instructor/courses/[courseId]/edit</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>講座情報更新
 承認申請は INS-UI-17（最終確認）から送信する。</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>instructor</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>INS-UI-06</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>講座シラバス編集</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>/instructor/courses/[courseId]/syllabus</t>
-        </is>
-      </c>
-      <c r="E27" s="36" t="inlineStr">
-        <is>
-          <t>セクション・レッスン構造編集</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>instructor</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>INS-UI-07</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>講座レッスン作成</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>/instructor/courses/[courseId]/lessons</t>
-        </is>
-      </c>
-      <c r="E28" s="36" t="inlineStr">
-        <is>
-          <t>レッスン内容表示（動画・テキスト）</t>
-        </is>
-      </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
           <t>instructor</t>
@@ -39834,7 +40019,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-08</t>
+          <t>INS-UI-09</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -39844,17 +40029,17 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>講座レッスン編集</t>
+          <t>カリキュラム・日程設定</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/lessons/[lessonId]/edit</t>
+          <t>/instructor/courses/[courseId]/schedule</t>
         </is>
       </c>
       <c r="E29" s="36" t="inlineStr">
         <is>
-          <t>レッスン内容表示（動画・テキスト）</t>
+          <t>ライブ配信スケジュール設定</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -39866,7 +40051,7 @@
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-09</t>
+          <t>INS-UI-10</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
@@ -39876,17 +40061,17 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>カリキュラム・日程設定</t>
+          <t>講座受講者管理</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/schedule</t>
+          <t>/instructor/courses/[courseId]/students</t>
         </is>
       </c>
       <c r="E30" s="36" t="inlineStr">
         <is>
-          <t>ライブ配信スケジュール設定</t>
+          <t>レッスン閲覧、進捗記録</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -39898,7 +40083,7 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-10</t>
+          <t>INS-UI-11</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -39908,17 +40093,17 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>講座受講者管理</t>
+          <t>課題提出状況一覧・評価</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/students</t>
+          <t>/instructor/courses/[courseId]/assignments</t>
         </is>
       </c>
       <c r="E31" s="36" t="inlineStr">
         <is>
-          <t>レッスン閲覧、進捗記録</t>
+          <t>提出一覧、採点、フィードバック</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -39930,7 +40115,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-11</t>
+          <t>INS-UI-12</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
@@ -39940,17 +40125,17 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>課題提出状況一覧・評価</t>
+          <t>課題詳細評価</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/assignments</t>
+          <t>/instructor/courses/[courseId]/lessons/[lessonId]/assignments</t>
         </is>
       </c>
       <c r="E32" s="36" t="inlineStr">
         <is>
-          <t>提出一覧、採点、フィードバック</t>
+          <t>課題内容、提出フォーム、採点結果</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -39962,7 +40147,7 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-12</t>
+          <t>INS-UI-13</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -39972,17 +40157,17 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>課題詳細評価</t>
+          <t>アンケート設計・集計</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/lessons/[lessonId]/assignments</t>
+          <t>/instructor/courses/[courseId]/surveys</t>
         </is>
       </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
-          <t>課題内容、提出フォーム、採点結果</t>
+          <t>アンケート回答フォーム</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -39994,7 +40179,7 @@
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-13</t>
+          <t>INS-UI-14</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
@@ -40004,29 +40189,29 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>アンケート設計・集計</t>
+          <t>講座チャット設定</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/surveys</t>
+          <t>/instructor/courses/[courseId]/chat/settings</t>
         </is>
       </c>
       <c r="E34" s="36" t="inlineStr">
         <is>
-          <t>アンケート回答フォーム</t>
+          <t>リアルタイムチャット、スレッド機能</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>instructor</t>
+          <t>instructor_owner</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-14</t>
+          <t>INS-UI-15</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -40036,29 +40221,30 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>講座チャット設定</t>
+          <t>収益管理（講師）</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/chat/settings</t>
+          <t>/instructor/analytics</t>
         </is>
       </c>
       <c r="E35" s="36" t="inlineStr">
         <is>
-          <t>リアルタイムチャット、スレッド機能</t>
+          <t>売上分析、振込先設定
+設定メニューの支払いタブ（STU-UI-13）の「受取（講師）」からも遷移可能（暫定導線）。</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>instructor_owner</t>
+          <t>instructor</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>INS-UI-15</t>
+          <t>INS-UI-16</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
@@ -40068,62 +40254,61 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>収益管理（講師）</t>
+          <t>講座設定（詳細）</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>/instructor/analytics</t>
+          <t>/instructor/courses/[courseId]/settings</t>
         </is>
       </c>
       <c r="E36" s="36" t="inlineStr">
         <is>
-          <t>売上分析、振込先設定
-設定メニューの支払いタブ（STU-UI-13）の「受取（講師）」からも遷移可能（暫定導線）。</t>
+          <t>公開設定、受講者管理</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
+          <t>instructor_owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INS-UI-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>講座作成（1on1/セミナー）</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>/instructor/courses/new/simple</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1on1/セミナー共通の講座作成画面。スタイルに応じて日程設定UIが条件分岐する（1on1: 15分/30分/60分枠、セミナー: 複数回・15分刻み）。サムネイル、タイトル、日程、金額、LP項目（必要性/解決すること/前提条件/おすすめ）を1画面で入力し、承認申請または限定公開を実行する。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>instructor</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>INS-UI-16</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>講座設定（詳細）</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>/instructor/courses/[courseId]/settings</t>
-        </is>
-      </c>
-      <c r="E37" s="36" t="inlineStr">
-        <is>
-          <t>公開設定、受講者管理</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>instructor_owner</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INS-UI-17</t>
+          <t>INS-UI-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -40133,221 +40318,221 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>講座承認申請（ブートキャンプ）</t>
+          <t>講座作成（ブートキャンプ STEP1: 基本情報・LP）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>/instructor/courses/[courseId]/request-approval</t>
+          <t>/instructor/courses/new/bootcamp</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ブートキャンプ作成フローの終端。申請内容の最終確認後、承認申請を送信する（API-030）。送信後はステータスが pending_approval となる。</t>
+          <t>ブートキャンプ講座作成の第1ステップ。サムネイル、タイトル・サブタイトル、メイン講師、サブ講師、金額、開催期間、申し込み期日、LP項目（必要性/解決すること/前提条件/おすすめ/講師紹介/FAQ）を入力する。完了後STEP2へ遷移。</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INS-UI-20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>講座作成（ブートキャンプ STEP2: シラバス・レッスン構成）</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/syllabus</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座作成の第2ステップ。セクション（週単位等）の追加・編集と、各セクション内のレッスン一覧表示。レッスン選択でINS-UI-21へ遷移。作成後のドラフト編集にも再利用する。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INS-UI-21</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>講座作成（ブートキャンプ STEP2: レッスン編集）</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/lessons/[lessonId]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ブートキャンプのレッスン編集画面。レッスンタイプ（座学/動画/ライブ・イベント/課題）に応じてフォームが切り替わる。座学: リッチテキスト、動画: アップロード/埋め込み、ライブ: 日時+URL、課題: 提出期限+確認期限。作成後のドラフト編集にも再利用する。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>INS-UI-22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>講座作成（ブートキャンプ STEP3: 公開設定・承認申請）</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/publish</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座作成の第3ステップ（最終確認）。講座サマリー（タイトル、開催期間、申し込み期日、定員数、料金）を表示し、プレビュー確認後に「範囲を限定して公開する」または「承認申請する」を実行する。承認申請はAPI-030、公開はAPI-031。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>instructor_owner</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-01</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>運営ログイン</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>/login</t>
-        </is>
-      </c>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t>auth.adapt-co.ioへのOIDCリダイレクト型ログイン</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-02</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>運営ダッシュボード</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>/admin/dashboard</t>
-        </is>
-      </c>
-      <c r="E40" s="36" t="inlineStr">
-        <is>
-          <t>KPI集計（受講者数・講師数・講座数・今月売上）、売上推移チャート（7D/1M/6M/1Y切替）、承認待ち講座リスト、最近のアクティビティ（監査ログ）。API: API-ADMIN-22（KPI）、API-ADMIN-23（売上推移）、API-ADMIN-24（アクティビティ）、API-ADMIN-01（承認待ち講座）。</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-03</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>受講者管理一覧</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>/admin/learners</t>
-        </is>
-      </c>
-      <c r="E41" s="36" t="inlineStr">
-        <is>
-          <t>全受講者リスト、凍結。「受講者を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-04</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>受講者詳細</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>/admin/learners/[userId]</t>
-        </is>
-      </c>
-      <c r="E42" s="36" t="inlineStr">
-        <is>
-          <t>受講履歴、決済履歴</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>INS-UI-23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ブートキャンプ運営（ホーム・通知）</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/home</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座の運営ホーム画面。講座固有サイドバー（ホーム/通知/提出物管理/カリキュラム確認/参加者一覧/コミュニティチャット）を持つ。通知一覧を表示する。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>instructor</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-05</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>講師管理一覧</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>/admin/instructors</t>
-        </is>
-      </c>
-      <c r="E43" s="36" t="inlineStr">
-        <is>
-          <t>全講師リスト、審査。「講師を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>INS-UI-24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ブートキャンプ運営（提出物管理）</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/submissions</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座の提出物管理画面。受講者別の進捗状況（全体進捗/課題提出状況）、最終提出日時を一覧表示し、提出物の確認へ遷移する。</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>instructor</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>ADM-UI-06</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>講師詳細</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>/admin/instructors/[userId]</t>
-        </is>
-      </c>
-      <c r="E44" s="36" t="inlineStr">
-        <is>
-          <t>開講講座、収益</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>operator,root_operator</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>INS-UI-25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ブートキャンプ運営（コミュニティチャット）</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>/instructor/courses/[courseId]/bootcamp/chat</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ブートキャンプ講座のコミュニティチャット画面。講座固有サイドバー内のチャンネル（管理者ページ/講師からのお知らせ/全体チャット/自己紹介/Q&amp;A/課題/講師チャット）でスレッド形式のコミュニケーションを行う。</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>instructor</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-07</t>
+          <t>ADM-UI-01</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
@@ -40357,29 +40542,29 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>一般運営ユーザー一覧</t>
+          <t>運営ログイン</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>/admin/operators</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
-          <t>運営スタッフ管理</t>
+          <t>auth.adapt-co.ioへのOIDCリダイレクト型ログイン</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>root_operator</t>
+          <t>operator,root_operator</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-08</t>
+          <t>ADM-UI-02</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
@@ -40389,29 +40574,29 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>一般運営ユーザー追加</t>
+          <t>運営ダッシュボード</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>/admin/operators/new</t>
+          <t>/admin/dashboard</t>
         </is>
       </c>
       <c r="E46" s="36" t="inlineStr">
         <is>
-          <t>メール招待による運営スタッフ追加。root_operatorがメールアドレスと付与ロール(operator/root_operator)を指定して招待メールを送信。招待されたユーザーはauth.adapt-co.io(Keycloak)でアカウント作成・パスワード設定を行いログイン可能となる。learner/instructorからの昇格ではない。</t>
+          <t>KPI集計（受講者数・講師数・講座数・今月売上）、売上推移チャート（7D/1M/6M/1Y切替）、承認待ち講座リスト、最近のアクティビティ（監査ログ）。API: API-ADMIN-22（KPI）、API-ADMIN-23（売上推移）、API-ADMIN-24（アクティビティ）、API-ADMIN-01（承認待ち講座）。</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>root_operator</t>
+          <t>operator,root_operator</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-09</t>
+          <t>ADM-UI-03</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -40421,29 +40606,29 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>一般運営ユーザー編集</t>
+          <t>受講者管理一覧</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>/admin/operators/[userId]</t>
+          <t>/admin/learners</t>
         </is>
       </c>
       <c r="E47" s="36" t="inlineStr">
         <is>
-          <t>運営スタッフ管理</t>
+          <t>全受講者リスト、凍結。「受講者を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>root_operator</t>
+          <t>operator,root_operator</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-10</t>
+          <t>ADM-UI-04</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
@@ -40453,17 +40638,17 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>講座一覧（全体）</t>
+          <t>受講者詳細</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>/admin/courses</t>
+          <t>/admin/learners/[userId]</t>
         </is>
       </c>
       <c r="E48" s="36" t="inlineStr">
         <is>
-          <t>講座一覧（全体）画面</t>
+          <t>受講履歴、決済履歴</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -40473,64 +40658,64 @@
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="62" t="inlineStr">
-        <is>
-          <t>ADM-UI-11</t>
-        </is>
-      </c>
-      <c r="B49" s="62" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>ADM-UI-05</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C49" s="62" t="inlineStr">
-        <is>
-          <t>講座代理作成（運営）</t>
-        </is>
-      </c>
-      <c r="D49" s="62" t="inlineStr">
-        <is>
-          <t>/admin/courses/new</t>
-        </is>
-      </c>
-      <c r="E49" s="63" t="inlineStr">
-        <is>
-          <t>運営による講座代理作成。講師側の講座作成画面と共通構成（サイドメニューは別）。ownerUserId（講師）を指定して作成。</t>
-        </is>
-      </c>
-      <c r="F49" s="62" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>講師管理一覧</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>/admin/instructors</t>
+        </is>
+      </c>
+      <c r="E49" s="36" t="inlineStr">
+        <is>
+          <t>全講師リスト、審査。「講師を招待」ボタンからモーダルダイアログでメール招待（API-ADMIN-10）。招待フローは運営スタッフ（ADM-UI-08）と同一方式。</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>operator,root_operator</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="62" t="inlineStr">
-        <is>
-          <t>ADM-UI-12</t>
-        </is>
-      </c>
-      <c r="B50" s="62" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>ADM-UI-06</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C50" s="62" t="inlineStr">
-        <is>
-          <t>講座代理編集（運営）</t>
-        </is>
-      </c>
-      <c r="D50" s="62" t="inlineStr">
-        <is>
-          <t>/admin/courses/[courseId]/edit</t>
-        </is>
-      </c>
-      <c r="E50" s="63" t="inlineStr">
-        <is>
-          <t>運営による講座代理編集。講師側の講座編集画面と共通構成（サイドメニューは別）。title, description, catalogVisibility, visibility, ownerUserId を変更可能。</t>
-        </is>
-      </c>
-      <c r="F50" s="62" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>講師詳細</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>/admin/instructors/[userId]</t>
+        </is>
+      </c>
+      <c r="E50" s="36" t="inlineStr">
+        <is>
+          <t>開講講座、収益</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>operator,root_operator</t>
         </is>
@@ -40539,7 +40724,7 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-13</t>
+          <t>ADM-UI-07</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -40549,29 +40734,29 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>講座詳細（監査）</t>
+          <t>一般運営ユーザー一覧</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>/admin/courses/[courseId]</t>
+          <t>/admin/operators</t>
         </is>
       </c>
       <c r="E51" s="36" t="inlineStr">
         <is>
-          <t>講座詳細（監査/審査）。講座詳細情報、シラバス、申請状況を確認し、審査パネルから承認/差し戻しを実施する（API-ADMIN-05）。審査操作は監査ログ対象。</t>
+          <t>運営スタッフ管理</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>operator,root_operator</t>
+          <t>root_operator</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-14</t>
+          <t>ADM-UI-08</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -40581,29 +40766,29 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>売上・決済管理</t>
+          <t>一般運営ユーザー追加</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>/admin/finance/overview</t>
+          <t>/admin/operators/new</t>
         </is>
       </c>
       <c r="E52" s="36" t="inlineStr">
         <is>
-          <t>決済履歴、手数料管理</t>
+          <t>メール招待による運営スタッフ追加。root_operatorがメールアドレスと付与ロール(operator/root_operator)を指定して招待メールを送信。招待されたユーザーはauth.adapt-co.io(Keycloak)でアカウント作成・パスワード設定を行いログイン可能となる。learner/instructorからの昇格ではない。</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>operator,root_operator</t>
+          <t>root_operator</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>ADM-UI-15</t>
+          <t>ADM-UI-09</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -40613,17 +40798,17 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>システム設定</t>
+          <t>一般運営ユーザー編集</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>/admin/settings/system</t>
+          <t>/admin/operators/[userId]</t>
         </is>
       </c>
       <c r="E53" s="36" t="inlineStr">
         <is>
-          <t>プラットフォーム設定</t>
+          <t>運営スタッフ管理</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -40635,149 +40820,297 @@
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
+          <t>ADM-UI-10</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>講座一覧（全体）</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>/admin/courses</t>
+        </is>
+      </c>
+      <c r="E54" s="36" t="inlineStr">
+        <is>
+          <t>講座一覧（全体）画面</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>operator,root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="inlineStr">
+        <is>
+          <t>ADM-UI-11</t>
+        </is>
+      </c>
+      <c r="B55" s="62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C55" s="62" t="inlineStr">
+        <is>
+          <t>講座代理作成（運営）</t>
+        </is>
+      </c>
+      <c r="D55" s="62" t="inlineStr">
+        <is>
+          <t>/admin/courses/new</t>
+        </is>
+      </c>
+      <c r="E55" s="63" t="inlineStr">
+        <is>
+          <t>運営による講座代理作成。講師側の講座作成画面と共通構成（サイドメニューは別）。ownerUserId（講師）を指定して作成。</t>
+        </is>
+      </c>
+      <c r="F55" s="62" t="inlineStr">
+        <is>
+          <t>operator,root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="inlineStr">
+        <is>
+          <t>ADM-UI-12</t>
+        </is>
+      </c>
+      <c r="B56" s="62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C56" s="62" t="inlineStr">
+        <is>
+          <t>講座代理編集（運営）</t>
+        </is>
+      </c>
+      <c r="D56" s="62" t="inlineStr">
+        <is>
+          <t>/admin/courses/[courseId]/edit</t>
+        </is>
+      </c>
+      <c r="E56" s="63" t="inlineStr">
+        <is>
+          <t>運営による講座代理編集。講師側の講座編集画面と共通構成（サイドメニューは別）。title, description, catalogVisibility, visibility, ownerUserId を変更可能。</t>
+        </is>
+      </c>
+      <c r="F56" s="62" t="inlineStr">
+        <is>
+          <t>operator,root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>ADM-UI-13</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>講座詳細（監査）</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>/admin/courses/[courseId]</t>
+        </is>
+      </c>
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>講座詳細（監査/審査）。講座詳細情報、シラバス、申請状況を確認し、審査パネルから承認/差し戻しを実施する（API-ADMIN-05）。審査操作は監査ログ対象。</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>operator,root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>ADM-UI-14</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>売上・決済管理</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>/admin/finance/overview</t>
+        </is>
+      </c>
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t>決済履歴、手数料管理</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>operator,root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>ADM-UI-15</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>システム設定</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>/admin/settings/system</t>
+        </is>
+      </c>
+      <c r="E59" s="36" t="inlineStr">
+        <is>
+          <t>プラットフォーム設定</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>root_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
           <t>ADM-UI-16</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>監査ログ</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>/admin/audit-logs</t>
         </is>
       </c>
-      <c r="E54" s="36" t="inlineStr">
+      <c r="E60" s="36" t="inlineStr">
         <is>
           <t>凍結・削除履歴</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>root_operator</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="64" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="64" t="inlineStr">
         <is>
           <t>AUTH-UI-01</t>
         </is>
       </c>
-      <c r="B55" s="64" t="inlineStr">
+      <c r="B61" s="64" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C61" s="64" t="inlineStr">
         <is>
           <t>（Auth）パスワードリセット申請画面</t>
         </is>
       </c>
-      <c r="D55" s="64" t="inlineStr">
+      <c r="D61" s="64" t="inlineStr">
         <is>
           <t>/realms/adapt/login-actions/reset-credentials</t>
         </is>
       </c>
-      <c r="E55" s="64" t="inlineStr">
+      <c r="E61" s="64" t="inlineStr">
         <is>
           <t>メールアドレス入力→リセットメール送信。アカウント有無を明示しない。auth.adapt-co.io管理画面。App側実装なし（リンク導線のみ）</t>
         </is>
       </c>
-      <c r="F55" s="64" t="inlineStr">
+      <c r="F61" s="64" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="65" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="65" t="inlineStr">
         <is>
           <t>AUTH-UI-02</t>
         </is>
       </c>
-      <c r="B56" s="65" t="inlineStr">
+      <c r="B62" s="65" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C56" s="65" t="inlineStr">
+      <c r="C62" s="65" t="inlineStr">
         <is>
           <t>（Auth）パスワード再設定画面</t>
         </is>
       </c>
-      <c r="D56" s="65" t="inlineStr">
+      <c r="D62" s="65" t="inlineStr">
         <is>
           <t>/realms/adapt/login-actions/action-token</t>
         </is>
       </c>
-      <c r="E56" s="65" t="inlineStr">
+      <c r="E62" s="65" t="inlineStr">
         <is>
           <t>リセットメール内リンク（token付き）からの遷移。新パスワード入力・確認。token有効期限24時間・ワンタイム。無効/期限切れ時は再発行へ誘導。完了後ログイン画面へ遷移。auth.adapt-co.io管理画面。App側実装なし（リンク導線のみ）</t>
         </is>
       </c>
-      <c r="F56" s="65" t="inlineStr">
+      <c r="F62" s="65" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="17" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="17" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="17" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="n"/>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="17" t="n"/>
-      <c r="D60" s="17" t="n"/>
-      <c r="F60" s="17" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="17" t="n"/>
-      <c r="D61" s="17" t="n"/>
-      <c r="F61" s="17" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="17" t="n"/>
-      <c r="C62" s="17" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="F62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n"/>
       <c r="B63" s="17" t="n"/>
       <c r="C63" s="17" t="n"/>
       <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
       <c r="F63" s="17" t="n"/>
     </row>
     <row r="64">
@@ -40785,6 +41118,7 @@
       <c r="B64" s="17" t="n"/>
       <c r="C64" s="17" t="n"/>
       <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
       <c r="F64" s="17" t="n"/>
     </row>
     <row r="65">
@@ -40792,6 +41126,7 @@
       <c r="B65" s="17" t="n"/>
       <c r="C65" s="17" t="n"/>
       <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
       <c r="F65" s="17" t="n"/>
     </row>
     <row r="66">
@@ -41073,6 +41408,48 @@
       <c r="C105" s="17" t="n"/>
       <c r="D105" s="17" t="n"/>
       <c r="F105" s="17" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="n"/>
+      <c r="B106" s="17" t="n"/>
+      <c r="C106" s="17" t="n"/>
+      <c r="D106" s="17" t="n"/>
+      <c r="F106" s="17" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="n"/>
+      <c r="B107" s="17" t="n"/>
+      <c r="C107" s="17" t="n"/>
+      <c r="D107" s="17" t="n"/>
+      <c r="F107" s="17" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="n"/>
+      <c r="B108" s="17" t="n"/>
+      <c r="C108" s="17" t="n"/>
+      <c r="D108" s="17" t="n"/>
+      <c r="F108" s="17" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="n"/>
+      <c r="B109" s="17" t="n"/>
+      <c r="C109" s="17" t="n"/>
+      <c r="D109" s="17" t="n"/>
+      <c r="F109" s="17" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="n"/>
+      <c r="B110" s="17" t="n"/>
+      <c r="C110" s="17" t="n"/>
+      <c r="D110" s="17" t="n"/>
+      <c r="F110" s="17" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="F111" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -24356,12 +24356,12 @@
       </c>
       <c r="C17" s="55" t="inlineStr">
         <is>
-          <t>STU-UI-15</t>
+          <t>STU-UI-14, STU-UI-15</t>
         </is>
       </c>
       <c r="D17" s="55" t="inlineStr">
         <is>
-          <t>Lesson</t>
+          <t>Lesson, CourseSection</t>
         </is>
       </c>
       <c r="E17" s="55" t="inlineStr">
@@ -31203,7 +31203,7 @@
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>SCR-INS-UI-06</t>
+          <t>SCR-INS-UI-20</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
@@ -31213,22 +31213,22 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>講座シラバス編集（画面機能）</t>
+          <t>講座作成（ブートキャンプ STEP2: シラバス・レッスン構成）（画面機能）</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>講座シラバス編集</t>
+          <t>講座作成（ブートキャンプ STEP2: シラバス・レッスン構成）</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>シラバスセクションの作成・編集、ブートキャンプのみ</t>
+          <t>セクション（週単位等）の追加・編集と、各セクション内のレッスン一覧表示。レッスン選択でINS-UI-21へ遷移。作成後のドラフト編集にも再利用する。</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>INS-UI-06</t>
+          <t>INS-UI-20</t>
         </is>
       </c>
       <c r="G73" s="15" t="inlineStr">
@@ -31245,7 +31245,7 @@
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>SCR-INS-UI-07</t>
+          <t>SCR-INS-UI-21</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
@@ -31255,22 +31255,22 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン作成（画面機能）</t>
+          <t>講座作成（ブートキャンプ STEP2: レッスン編集 — 作成）（画面機能）</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン作成</t>
+          <t>講座作成（ブートキャンプ STEP2: レッスン編集 — 新規作成）</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>セクションに紐づくレッスン作成、レッスンタイプ(座学/動画/ライブ・イベント/課題)、ブートキャンプのみ</t>
+          <t>ブートキャンプのレッスン新規作成。レッスンタイプ（座学/動画/ライブ・イベント/課題）に応じてフォームが切り替わる。</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>INS-UI-07</t>
+          <t>INS-UI-21</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -31287,7 +31287,7 @@
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>SCR-INS-UI-08</t>
+          <t>SCR-INS-UI-21</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
@@ -31297,22 +31297,22 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン編集（画面機能）</t>
+          <t>講座作成（ブートキャンプ STEP2: レッスン編集 — 編集）（画面機能）</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン編集</t>
+          <t>講座作成（ブートキャンプ STEP2: レッスン編集 — 既存編集）</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>レッスン編集</t>
+          <t>ブートキャンプのレッスン既存編集。作成後のドラフト編集にも再利用する。</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>INS-UI-08</t>
+          <t>INS-UI-21</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
@@ -31665,7 +31665,7 @@
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>SCR-STU-UI-03-1</t>
+          <t>SCR-STU-UI-15</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
@@ -31675,22 +31675,22 @@
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン閲覧（画面機能）</t>
+          <t>ブートキャンプ受講（レッスン閲覧）（画面機能）</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>講座レッスン詳細の閲覧</t>
+          <t>ブートキャンプ受講（レッスン閲覧）</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>講座内レッスン（座学/動画/ライブ・イベント/課題）の詳細を表示し、進捗状況を表示する。課題レッスンは課題スレッドへ導線を提供する。</t>
+          <t>ブートキャンプ講座のレッスン閲覧画面。レッスンタイプ（座学/動画/ライブ・イベント）に応じた表示を行う。</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>STU-UI-03-1</t>
+          <t>STU-UI-15</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -34203,7 +34203,7 @@
       </c>
       <c r="J15" s="45" t="inlineStr">
         <is>
-          <t>GenericDetailView</t>
+          <t>LearnerCourseDetailView</t>
         </is>
       </c>
       <c r="K15" s="45" t="inlineStr">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="J17" s="45" t="inlineStr">
         <is>
-          <t>GenericListResponse</t>
+          <t>LearnerSideMenuView</t>
         </is>
       </c>
       <c r="K17" s="45" t="inlineStr">
@@ -35503,7 +35503,7 @@
       </c>
       <c r="J35" s="45" t="inlineStr">
         <is>
-          <t>CourseDetailView</t>
+          <t>SyllabusView</t>
         </is>
       </c>
       <c r="K35" s="45" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="J36" s="45" t="inlineStr">
         <is>
-          <t>CourseDetailView</t>
+          <t>SyllabusView</t>
         </is>
       </c>
       <c r="K36" s="45" t="inlineStr">
@@ -40006,8 +40006,9 @@
       </c>
       <c r="E28" s="36" t="inlineStr">
         <is>
-          <t>講座情報更新
-承認申請は INS-UI-17（最終確認）から送信する。</t>
+          <t>講座情報更新（1on1/セミナー）。
+ブートキャンプの承認申請は INS-UI-22（公開設定・承認申請）から送信する。
+1on1/セミナーは本画面から直接承認申請する。</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -36088,7 +36088,7 @@
       </c>
       <c r="J44" s="45" t="inlineStr">
         <is>
-          <t>CourseDetailView</t>
+          <t>SubmissionListResponse</t>
         </is>
       </c>
       <c r="K44" s="45" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="J46" s="45" t="inlineStr">
         <is>
-          <t>CourseDetailView</t>
+          <t>CourseMemberListResponse</t>
         </is>
       </c>
       <c r="K46" s="45" t="inlineStr">

--- a/docs/design/adapt_基本設計_最終版.xlsx
+++ b/docs/design/adapt_基本設計_最終版.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32000" yWindow="500" windowWidth="32000" windowHeight="35500" tabRatio="600" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_機能要件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_非機能要件" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_技術スタック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ディレクトリ構造" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_API一覧" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_画面一覧" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Enums定義" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_DB_テーブル一覧" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_DB_カラム定義" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_リレーション定義" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_インデックス定義" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_権限マトリクス" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_権限マトリクス_拡張" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_トレーサビリティ" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_コース・ライフサイクル" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_変更履歴" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_Prisma実装ガイド" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="01_概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_機能要件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_非機能要件" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_技術スタック" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_ディレクトリ構造" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_API一覧" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_画面一覧" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_Enums定義" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_DB_テーブル一覧" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_DB_カラム定義" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_リレーション定義" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_インデックス定義" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_権限マトリクス" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_権限マトリクス_拡張" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_トレーサビリティ" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_コース・ライフサイクル" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="99_変更履歴" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_Prisma実装ガイド" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="J11" s="45" t="inlineStr">
         <is>
-          <t>GenericDetailView</t>
+          <t>StoreCourseDetailView</t>
         </is>
       </c>
       <c r="K11" s="45" t="inlineStr">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="J14" s="45" t="inlineStr">
         <is>
-          <t>GenericListResponse</t>
+          <t>CourseListResponse</t>
         </is>
       </c>
       <c r="K14" s="45" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="J21" s="45" t="inlineStr">
         <is>
-          <t>GenericListResponse</t>
+          <t>LearnerRecordListResponse</t>
         </is>
       </c>
       <c r="K21" s="45" t="inlineStr">
